--- a/ig/ch-elm/CodeSystem-ch-elm-results-completion-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-results-completion-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -138,15 +138,9 @@
     <t>1</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-bot-spec</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-complete-spec</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-diph-spec</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-geni-spec</t>
   </si>
   <si>
@@ -156,18 +150,9 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-sterile-spec</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-tub-spec</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-bot-org</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-bru-org</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-camp-diar-org</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-camp-org</t>
   </si>
   <si>
@@ -180,12 +165,6 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-diph-org</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-ebol-org</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-ehec-org</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-ehec-tox-org</t>
   </si>
   <si>
@@ -195,12 +174,6 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-hanta-org</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-hiv-org</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-inf-org</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-influenza-hxny-org</t>
   </si>
   <si>
@@ -225,15 +198,6 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-mpox-org</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-mpx-ctng</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-mpx-sash</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-mpx-sashec</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-pneu-org</t>
   </si>
   <si>
@@ -243,10 +207,10 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-sal-org-complete</t>
   </si>
   <si>
+    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-shi-nent-org</t>
+  </si>
+  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-shi-org</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-tub-gen-org</t>
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-tub-org</t>
@@ -565,7 +529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -862,126 +826,6 @@
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
     </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/ch-elm/CodeSystem-ch-elm-results-completion-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-results-completion-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-diph-org</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-ehec-tox-org</t>
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-haem-org</t>
@@ -529,7 +526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -816,16 +813,6 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/ch-elm/CodeSystem-ch-elm-results-completion-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-results-completion-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/CodeSystem-ch-elm-results-completion-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-results-completion-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
